--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3157894736842105</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="B2">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3591549295774648</v>
+        <v>0.352112676056338</v>
       </c>
       <c r="D2">
-        <v>0.7844827586206896</v>
+        <v>0.8288288288288288</v>
       </c>
       <c r="E2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
